--- a/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFVA.xlsx
+++ b/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFVA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F9FDED-0620-4860-889E-5A4A042DB8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA043E58-E16A-46B9-AAE7-E5CFC92C24C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -291,16 +291,16 @@
     <t>Group</t>
   </si>
   <si>
-    <t>Liz Hedgcock</t>
-  </si>
-  <si>
-    <t>Opp Approver</t>
-  </si>
-  <si>
     <t>Indrajeet Singh</t>
   </si>
   <si>
     <t>System Admin</t>
+  </si>
+  <si>
+    <t>Blaise Brunda</t>
+  </si>
+  <si>
+    <t>Conversion FVA</t>
   </si>
 </sst>
 </file>
@@ -1069,6 +1069,7 @@
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1084,21 +1085,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">

--- a/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFVA.xlsx
+++ b/TestData/LV_TMTC0036078_TMTC0036082_VerifyTheMappingOfComplianceAndLegalFieldsFromOpportunityToEngagementFVA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA043E58-E16A-46B9-AAE7-E5CFC92C24C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7444363-42DE-40EF-8E34-D986C603AD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="88">
   <si>
     <t>User</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>Conversion FVA</t>
+  </si>
+  <si>
+    <t>LocationBenefit</t>
+  </si>
+  <si>
+    <t>Benefit is likely &gt;75% outside the US</t>
   </si>
 </sst>
 </file>
@@ -1277,6 +1283,9 @@
       <c r="AD1" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1369,8 +1378,8 @@
       <c r="AD2" t="s">
         <v>53</v>
       </c>
-      <c r="AE2">
-        <v>1</v>
+      <c r="AE2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
